--- a/e2e-screenshots/accessory-stock/sales-accessory.xlsx
+++ b/e2e-screenshots/accessory-stock/sales-accessory.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="AMAZON" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="README" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="AMAZON" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -47,18 +47,66 @@
     <t>Commission</t>
   </si>
   <si>
+    <t>C. VAT</t>
+  </si>
+  <si>
+    <t>DSF</t>
+  </si>
+  <si>
+    <t>DSF. VAT</t>
+  </si>
+  <si>
     <t>Postage</t>
   </si>
   <si>
+    <t>P. VAT</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Total VAT</t>
+  </si>
+  <si>
     <t>GP</t>
   </si>
   <si>
     <t>GP %</t>
   </si>
   <si>
+    <t>Total VAT NTP</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Return Date</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Return Reason</t>
+  </si>
+  <si>
+    <t>Shipping Legs</t>
+  </si>
+  <si>
+    <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Net GP £</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
     <t>2026-07-22</t>
   </si>
   <si>
@@ -74,95 +122,62 @@
     <t>MOBILE WHOLESALE LTD</t>
   </si>
   <si>
-    <t>AMAZON SALES — single-marketplace upload template</t>
-  </si>
-  <si>
-    <t>One sheet, AMAZON only. In Import → Sales Report, choose AMAZON before picking the file.</t>
-  </si>
-  <si>
-    <t>The sheet does not have to be named AMAZON — with a marketplace selected the first sheet is used, so a raw export works as-is.</t>
-  </si>
-  <si>
-    <t>Leave the derived money columns blank: SP-BP, tax, commission, VAT, GP and GP% are all recomputed by the app.</t>
-  </si>
-  <si>
-    <t>Record ids match the combined workbook exactly, so uploading per-channel today and a combined file later updates the same rows instead of duplicating them.</t>
-  </si>
-  <si>
-    <t>The grey example rows are illustrations — delete them before uploading your own data.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Accepted values / format</t>
-  </si>
-  <si>
-    <t>What the importer does with it</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t>Sale date — drives every period figure.</t>
-  </si>
-  <si>
-    <t>Free text</t>
-  </si>
-  <si>
-    <t>Marketplace order id. With the IMEI it forms the record key, so re-uploads update rather than duplicate.</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Fallback identifier when IMEI is blank.</t>
-  </si>
-  <si>
-    <t>15 digits, or several separated by " / "</t>
-  </si>
-  <si>
-    <t>Matches the sale to a unit in stock and marks it SOLD. Multi-IMEI cells split into one row per phone with BP/SP divided.</t>
-  </si>
-  <si>
-    <t>Needed only for sales with no matching unit, completed during import.</t>
-  </si>
-  <si>
-    <t>Number &gt; 0</t>
-  </si>
-  <si>
-    <t>Buy price.</t>
-  </si>
-  <si>
-    <t>Sale price as the marketplace reports it.</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>What postage actually cost.</t>
-  </si>
-  <si>
-    <t>(row colour)</t>
-  </si>
-  <si>
-    <t>Red fill on Date or Order</t>
-  </si>
-  <si>
-    <t>Imports the row as FLAGGED — the convention for returns, refunds, chargebacks and disputes.</t>
+    <t>SALES TEMPLATE — same columns as the Sales Report</t>
+  </si>
+  <si>
+    <t>What this is</t>
+  </si>
+  <si>
+    <t>One sheet per marketplace (AMAZON), with exactly the columns the Sales Report exports. This file is generated FROM that report, so the two cannot drift apart.</t>
+  </si>
+  <si>
+    <t>The formulas are live</t>
+  </si>
+  <si>
+    <t>Type a BP and an SP into a row and every derived column fills in immediately — SP-BP, Marginal Tax, Commission, the VAT lines, GP, GP % and Total VAT NTP. Rows you have not touched stay blank; they wake up as soon as the row has an SP.</t>
+  </si>
+  <si>
+    <t>What YOU fill in</t>
+  </si>
+  <si>
+    <t>Date, Order Number, SKU, IMEI, Supplier, Quantity, BP, SP and Postage. On eBay also Marketing and P. VAT, and on Temu the Commission the marketplace actually charged — those cells carry no formula in the operator master either, because no formula can reproduce a figure the marketplace invoices per order.</t>
+  </si>
+  <si>
+    <t>What you leave alone</t>
+  </si>
+  <si>
+    <t>Every other money column is a formula. Overwriting one replaces live maths with a frozen number that will not follow a price correction.</t>
+  </si>
+  <si>
+    <t>Row 2</t>
+  </si>
+  <si>
+    <t>A worked example, filled in so you can see the formulas computing. Delete it or type over it.</t>
+  </si>
+  <si>
+    <t>Running out of rows</t>
+  </si>
+  <si>
+    <t>200 rows come primed. For more, select the last row and drag its fill handle down — the formulas carry themselves.</t>
+  </si>
+  <si>
+    <t>The TOTAL row</t>
+  </si>
+  <si>
+    <t>At the foot of each sheet, summing the rows above it. If you drag past it, move it down.</t>
+  </si>
+  <si>
+    <t>Getting this back in</t>
+  </si>
+  <si>
+    <t>Sales are recorded in the app under Sell → Mark Sold (or Mark Multiple Sold for one order covering several handsets). This file is a working sheet and a record, not an upload route.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -172,37 +187,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <color rgb="FF475569"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFB91C1C"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF64748B"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -217,22 +213,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,115 +561,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="9" width="12" customWidth="1"/>
-    <col min="10" max="12" width="16" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3.5</v>
-      </c>
-      <c r="H2">
-        <v>8.99</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -688,186 +648,149 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF10B981"/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="74" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3.5</v>
+      </c>
+      <c r="H2">
+        <v>8.99</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="M2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>47</v>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-stock/sales-accessory.xlsx
+++ b/e2e-screenshots/accessory-stock/sales-accessory.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -26,6 +26,15 @@
     <t>IMEI</t>
   </si>
   <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
     <t>Supplier</t>
   </si>
   <si>
@@ -77,34 +86,25 @@
     <t>Total VAT NTP</t>
   </si>
   <si>
+    <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Net GP £</t>
+  </si>
+  <si>
+    <t>Return Date</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Shipping Legs</t>
+  </si>
+  <si>
+    <t>Return Reason</t>
+  </si>
+  <si>
     <t>Comments</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Return Date</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>Return Reason</t>
-  </si>
-  <si>
-    <t>Shipping Legs</t>
-  </si>
-  <si>
-    <t>Postage Loss</t>
-  </si>
-  <si>
-    <t>Net GP £</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>Colour</t>
   </si>
   <si>
     <t>2026-07-22</t>
@@ -746,7 +746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -759,38 +759,20 @@
       <c r="D2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>3.5</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>8.99</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2">
+      <c r="R2">
         <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-stock/sales-accessory.xlsx
+++ b/e2e-screenshots/accessory-stock/sales-accessory.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -71,7 +71,7 @@
     <t>P. VAT</t>
   </si>
   <si>
-    <t>Accessories</t>
+    <t>Acc</t>
   </si>
   <si>
     <t>Total VAT</t>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -570,74 +582,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -648,10 +660,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -745,22 +757,34 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I2">
         <v>2</v>
